--- a/Vignettes/ClimateHCRs/HCRshiny/data/HCR_par_shiny.xlsx
+++ b/Vignettes/ClimateHCRs/HCRshiny/data/HCR_par_shiny.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/KKH/Documents/GitHub_mac/ACLIM2/Vignettes/ClimateHCRs/HCRshiny/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0ECD8C6-751B-5D4C-93C0-E84FC25395D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB52B0C1-A9D8-3A48-9FCE-3AAF4B372B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{29601B6F-7A1C-B44B-9D68-D49A773C8A09}"/>
   </bookViews>
@@ -161,13 +161,13 @@
     <t>HCR8b: log_theta set to 0.75 + SSL</t>
   </si>
   <si>
-    <t>HCR10a: no offset + SSL</t>
+    <t>HCR10c: large offset + SSL</t>
   </si>
   <si>
-    <t>HCR10b: small offset + SSL</t>
+    <t>HCR10a: small offset + SSL</t>
   </si>
   <si>
-    <t>HCR10c: large offset + SSL</t>
+    <t>HCR10b: med offset + SSL</t>
   </si>
 </sst>
 </file>
@@ -5451,7 +5451,7 @@
         <v>18</v>
       </c>
       <c r="G211" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
@@ -5474,7 +5474,7 @@
         <v>18</v>
       </c>
       <c r="G212" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -5497,21 +5497,24 @@
         <v>18</v>
       </c>
       <c r="G213" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>38</v>
       </c>
-      <c r="B214" s="5">
-        <v>-1000000000</v>
-      </c>
-      <c r="C214" s="5">
-        <v>-1000000000</v>
-      </c>
-      <c r="D214" s="5">
-        <v>-1000000000</v>
+      <c r="B214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="C214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
+      </c>
+      <c r="D214">
+        <f>LN(0.5)</f>
+        <v>-0.69314718055994529</v>
       </c>
       <c r="E214">
         <v>10</v>
@@ -5520,7 +5523,7 @@
         <v>18</v>
       </c>
       <c r="G214" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -5543,7 +5546,7 @@
         <v>18</v>
       </c>
       <c r="G215" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -5566,7 +5569,7 @@
         <v>18</v>
       </c>
       <c r="G216" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
@@ -5589,7 +5592,7 @@
         <v>18</v>
       </c>
       <c r="G217" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
@@ -5612,7 +5615,7 @@
         <v>18</v>
       </c>
       <c r="G218" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -5635,7 +5638,7 @@
         <v>18</v>
       </c>
       <c r="G219" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -5658,7 +5661,7 @@
         <v>18</v>
       </c>
       <c r="G220" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
@@ -5681,7 +5684,7 @@
         <v>18</v>
       </c>
       <c r="G221" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -5704,7 +5707,7 @@
         <v>16</v>
       </c>
       <c r="G222" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -5727,7 +5730,7 @@
         <v>16</v>
       </c>
       <c r="G223" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -5750,7 +5753,7 @@
         <v>16</v>
       </c>
       <c r="G224" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
@@ -5758,16 +5761,16 @@
         <v>38</v>
       </c>
       <c r="B225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="C225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="D225">
-        <f>LN(0.25)</f>
-        <v>-1.3862943611198906</v>
+        <f>LN(1.5)</f>
+        <v>0.40546510810816438</v>
       </c>
       <c r="E225">
         <v>10</v>
@@ -5776,7 +5779,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
@@ -5799,7 +5802,7 @@
         <v>16</v>
       </c>
       <c r="G226" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -5822,7 +5825,7 @@
         <v>16</v>
       </c>
       <c r="G227" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -5845,7 +5848,7 @@
         <v>16</v>
       </c>
       <c r="G228" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -5868,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="G229" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -5891,7 +5894,7 @@
         <v>16</v>
       </c>
       <c r="G230" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -5914,7 +5917,7 @@
         <v>16</v>
       </c>
       <c r="G231" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -5937,7 +5940,7 @@
         <v>16</v>
       </c>
       <c r="G232" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -5960,7 +5963,7 @@
         <v>21</v>
       </c>
       <c r="G233" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -5983,7 +5986,7 @@
         <v>21</v>
       </c>
       <c r="G234" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -6006,7 +6009,7 @@
         <v>21</v>
       </c>
       <c r="G235" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -6014,16 +6017,16 @@
         <v>38</v>
       </c>
       <c r="B236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f>LN(3)</f>
+        <v>1.0986122886681098</v>
       </c>
       <c r="C236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f t="shared" ref="C236:D236" si="1">LN(3)</f>
+        <v>1.0986122886681098</v>
       </c>
       <c r="D236">
-        <f>LN(0.5)</f>
-        <v>-0.69314718055994529</v>
+        <f t="shared" si="1"/>
+        <v>1.0986122886681098</v>
       </c>
       <c r="E236">
         <v>10</v>
@@ -6032,7 +6035,7 @@
         <v>21</v>
       </c>
       <c r="G236" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6055,7 +6058,7 @@
         <v>21</v>
       </c>
       <c r="G237" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -6078,7 +6081,7 @@
         <v>21</v>
       </c>
       <c r="G238" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -6101,7 +6104,7 @@
         <v>21</v>
       </c>
       <c r="G239" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -6124,7 +6127,7 @@
         <v>21</v>
       </c>
       <c r="G240" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -6147,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="G241" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -6170,7 +6173,7 @@
         <v>21</v>
       </c>
       <c r="G242" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -6193,7 +6196,7 @@
         <v>21</v>
       </c>
       <c r="G243" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
